--- a/Лаба 2.xlsx
+++ b/Лаба 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivankosarev/Documents/ВУЗ/Программная инженерия/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE4F975D-C2A2-E04C-962D-D995D0DA1B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AD3387-D660-714E-B7A6-C5B9FD580BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="13">
   <si>
     <t>Имя</t>
   </si>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" ref="G6:G69" si="0">IF(AND(B6="Заполнено корректно",C6="Заполнено корректно",E6="Заполнено корректно"),"Регистрация пользователя","Пользовватель не заригестрирован")</f>
@@ -586,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
@@ -634,7 +634,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="0"/>
@@ -658,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="0"/>
@@ -706,7 +706,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="0"/>
@@ -730,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="0"/>
@@ -778,7 +778,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="0"/>
@@ -802,7 +802,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="0"/>
@@ -850,7 +850,7 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="0"/>
@@ -874,7 +874,7 @@
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="0"/>
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="0"/>
@@ -946,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="0"/>
@@ -994,7 +994,7 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="0"/>
@@ -1018,7 +1018,7 @@
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="0"/>
@@ -1066,7 +1066,7 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="0"/>
@@ -1090,7 +1090,7 @@
         <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="0"/>
@@ -1138,7 +1138,7 @@
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="0"/>
@@ -1162,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="0"/>
@@ -1210,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="0"/>
@@ -1234,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="0"/>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="0"/>
@@ -1306,7 +1306,7 @@
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="0"/>
@@ -1354,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="0"/>
@@ -1378,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="0"/>
@@ -1426,7 +1426,7 @@
         <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="0"/>
@@ -1450,7 +1450,7 @@
         <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="0"/>
@@ -1498,7 +1498,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="0"/>
@@ -1522,7 +1522,7 @@
         <v>5</v>
       </c>
       <c r="F46" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="0"/>
@@ -1570,7 +1570,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="0"/>
@@ -1594,7 +1594,7 @@
         <v>5</v>
       </c>
       <c r="F49" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="0"/>
@@ -1642,7 +1642,7 @@
         <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="0"/>
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="F52" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="0"/>
@@ -1714,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="F54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="0"/>
@@ -1738,7 +1738,7 @@
         <v>5</v>
       </c>
       <c r="F55" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G55" t="str">
         <f t="shared" si="0"/>
@@ -1786,7 +1786,7 @@
         <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="0"/>
@@ -1810,7 +1810,7 @@
         <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="0"/>
@@ -1821,15 +1821,45 @@
       <c r="A59">
         <v>55</v>
       </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" t="s">
+        <v>4</v>
+      </c>
       <c r="G59" t="str">
         <f t="shared" si="0"/>
-        <v>Пользовватель не заригестрирован</v>
+        <v>Регистрация пользователя</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>56</v>
       </c>
+      <c r="B60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" t="s">
+        <v>4</v>
+      </c>
       <c r="G60" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1839,6 +1869,21 @@
       <c r="A61">
         <v>57</v>
       </c>
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" t="s">
+        <v>4</v>
+      </c>
       <c r="G61" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1848,15 +1893,45 @@
       <c r="A62">
         <v>58</v>
       </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" t="s">
+        <v>4</v>
+      </c>
       <c r="G62" t="str">
         <f t="shared" si="0"/>
-        <v>Пользовватель не заригестрирован</v>
+        <v>Регистрация пользователя</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>59</v>
       </c>
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" t="s">
+        <v>4</v>
+      </c>
       <c r="G63" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1866,6 +1941,21 @@
       <c r="A64">
         <v>60</v>
       </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64" t="s">
+        <v>4</v>
+      </c>
       <c r="G64" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1875,6 +1965,21 @@
       <c r="A65">
         <v>61</v>
       </c>
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" t="s">
+        <v>4</v>
+      </c>
       <c r="G65" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1884,6 +1989,21 @@
       <c r="A66">
         <v>62</v>
       </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" t="s">
+        <v>4</v>
+      </c>
       <c r="G66" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1893,6 +2013,21 @@
       <c r="A67">
         <v>63</v>
       </c>
+      <c r="B67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" t="s">
+        <v>4</v>
+      </c>
       <c r="G67" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1902,6 +2037,21 @@
       <c r="A68">
         <v>64</v>
       </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" t="s">
+        <v>4</v>
+      </c>
       <c r="G68" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1911,6 +2061,21 @@
       <c r="A69">
         <v>65</v>
       </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" t="s">
+        <v>4</v>
+      </c>
       <c r="G69" t="str">
         <f t="shared" si="0"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1920,6 +2085,21 @@
       <c r="A70">
         <v>66</v>
       </c>
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" t="s">
+        <v>4</v>
+      </c>
       <c r="G70" t="str">
         <f t="shared" ref="G70:G133" si="1">IF(AND(B70="Заполнено корректно",C70="Заполнено корректно",E70="Заполнено корректно"),"Регистрация пользователя","Пользовватель не заригестрирован")</f>
         <v>Пользовватель не заригестрирован</v>
@@ -1929,6 +2109,21 @@
       <c r="A71">
         <v>67</v>
       </c>
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" t="s">
+        <v>4</v>
+      </c>
       <c r="G71" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1938,6 +2133,21 @@
       <c r="A72">
         <v>68</v>
       </c>
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" t="s">
+        <v>4</v>
+      </c>
       <c r="G72" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1947,6 +2157,21 @@
       <c r="A73">
         <v>69</v>
       </c>
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" t="s">
+        <v>5</v>
+      </c>
+      <c r="F73" t="s">
+        <v>4</v>
+      </c>
       <c r="G73" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1956,6 +2181,21 @@
       <c r="A74">
         <v>70</v>
       </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" t="s">
+        <v>4</v>
+      </c>
       <c r="G74" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1965,6 +2205,21 @@
       <c r="A75">
         <v>71</v>
       </c>
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" t="s">
+        <v>4</v>
+      </c>
       <c r="G75" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1974,6 +2229,21 @@
       <c r="A76">
         <v>72</v>
       </c>
+      <c r="B76" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" t="s">
+        <v>4</v>
+      </c>
       <c r="G76" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1983,6 +2253,21 @@
       <c r="A77">
         <v>73</v>
       </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" t="s">
+        <v>4</v>
+      </c>
       <c r="G77" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -1992,6 +2277,21 @@
       <c r="A78">
         <v>74</v>
       </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" t="s">
+        <v>4</v>
+      </c>
       <c r="G78" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2001,6 +2301,21 @@
       <c r="A79">
         <v>75</v>
       </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" t="s">
+        <v>4</v>
+      </c>
       <c r="G79" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2010,6 +2325,21 @@
       <c r="A80">
         <v>76</v>
       </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>4</v>
+      </c>
       <c r="G80" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2019,6 +2349,21 @@
       <c r="A81">
         <v>77</v>
       </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" t="s">
+        <v>4</v>
+      </c>
       <c r="G81" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2028,6 +2373,21 @@
       <c r="A82">
         <v>78</v>
       </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
+        <v>4</v>
+      </c>
       <c r="G82" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2037,6 +2397,21 @@
       <c r="A83">
         <v>79</v>
       </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" t="s">
+        <v>4</v>
+      </c>
       <c r="G83" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2046,6 +2421,21 @@
       <c r="A84">
         <v>80</v>
       </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" t="s">
+        <v>4</v>
+      </c>
       <c r="G84" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2055,6 +2445,21 @@
       <c r="A85">
         <v>81</v>
       </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" t="s">
+        <v>4</v>
+      </c>
       <c r="G85" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2064,6 +2469,21 @@
       <c r="A86">
         <v>82</v>
       </c>
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>4</v>
+      </c>
       <c r="G86" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2073,6 +2493,21 @@
       <c r="A87">
         <v>83</v>
       </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" t="s">
+        <v>4</v>
+      </c>
       <c r="G87" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2082,6 +2517,21 @@
       <c r="A88">
         <v>84</v>
       </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>4</v>
+      </c>
       <c r="G88" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2091,6 +2541,21 @@
       <c r="A89">
         <v>85</v>
       </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" t="s">
+        <v>4</v>
+      </c>
       <c r="G89" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2100,6 +2565,21 @@
       <c r="A90">
         <v>86</v>
       </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" t="s">
+        <v>4</v>
+      </c>
       <c r="G90" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2109,6 +2589,21 @@
       <c r="A91">
         <v>87</v>
       </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" t="s">
+        <v>4</v>
+      </c>
       <c r="G91" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2118,6 +2613,21 @@
       <c r="A92">
         <v>88</v>
       </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" t="s">
+        <v>3</v>
+      </c>
+      <c r="F92" t="s">
+        <v>4</v>
+      </c>
       <c r="G92" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2127,6 +2637,21 @@
       <c r="A93">
         <v>89</v>
       </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" t="s">
+        <v>4</v>
+      </c>
       <c r="G93" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2136,6 +2661,21 @@
       <c r="A94">
         <v>90</v>
       </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>4</v>
+      </c>
       <c r="G94" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2145,6 +2685,21 @@
       <c r="A95">
         <v>91</v>
       </c>
+      <c r="B95" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" t="s">
+        <v>4</v>
+      </c>
       <c r="G95" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2154,6 +2709,21 @@
       <c r="A96">
         <v>92</v>
       </c>
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" t="s">
+        <v>4</v>
+      </c>
       <c r="G96" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2163,6 +2733,21 @@
       <c r="A97">
         <v>93</v>
       </c>
+      <c r="B97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" t="s">
+        <v>5</v>
+      </c>
+      <c r="F97" t="s">
+        <v>4</v>
+      </c>
       <c r="G97" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2172,6 +2757,21 @@
       <c r="A98">
         <v>94</v>
       </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s">
+        <v>3</v>
+      </c>
+      <c r="F98" t="s">
+        <v>4</v>
+      </c>
       <c r="G98" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2181,6 +2781,21 @@
       <c r="A99">
         <v>95</v>
       </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>4</v>
+      </c>
+      <c r="F99" t="s">
+        <v>4</v>
+      </c>
       <c r="G99" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2190,6 +2805,21 @@
       <c r="A100">
         <v>96</v>
       </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" t="s">
+        <v>4</v>
+      </c>
       <c r="G100" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2199,6 +2829,21 @@
       <c r="A101">
         <v>97</v>
       </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" t="s">
+        <v>4</v>
+      </c>
       <c r="G101" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2208,6 +2853,21 @@
       <c r="A102">
         <v>98</v>
       </c>
+      <c r="B102" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" t="s">
+        <v>4</v>
+      </c>
       <c r="G102" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2217,6 +2877,21 @@
       <c r="A103">
         <v>99</v>
       </c>
+      <c r="B103" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" t="s">
+        <v>5</v>
+      </c>
+      <c r="F103" t="s">
+        <v>4</v>
+      </c>
       <c r="G103" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2226,6 +2901,21 @@
       <c r="A104">
         <v>100</v>
       </c>
+      <c r="B104" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s">
+        <v>3</v>
+      </c>
+      <c r="F104" t="s">
+        <v>4</v>
+      </c>
       <c r="G104" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2235,6 +2925,21 @@
       <c r="A105">
         <v>101</v>
       </c>
+      <c r="B105" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" t="s">
+        <v>4</v>
+      </c>
       <c r="G105" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2244,6 +2949,21 @@
       <c r="A106">
         <v>102</v>
       </c>
+      <c r="B106" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>5</v>
+      </c>
+      <c r="F106" t="s">
+        <v>4</v>
+      </c>
       <c r="G106" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2253,6 +2973,21 @@
       <c r="A107">
         <v>103</v>
       </c>
+      <c r="B107" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" t="s">
+        <v>3</v>
+      </c>
+      <c r="F107" t="s">
+        <v>4</v>
+      </c>
       <c r="G107" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2262,6 +2997,21 @@
       <c r="A108">
         <v>104</v>
       </c>
+      <c r="B108" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" t="s">
+        <v>4</v>
+      </c>
+      <c r="F108" t="s">
+        <v>4</v>
+      </c>
       <c r="G108" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2271,6 +3021,21 @@
       <c r="A109">
         <v>105</v>
       </c>
+      <c r="B109" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>4</v>
+      </c>
       <c r="G109" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2280,6 +3045,21 @@
       <c r="A110">
         <v>106</v>
       </c>
+      <c r="B110" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" t="s">
+        <v>3</v>
+      </c>
+      <c r="F110" t="s">
+        <v>4</v>
+      </c>
       <c r="G110" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2289,6 +3069,21 @@
       <c r="A111">
         <v>107</v>
       </c>
+      <c r="B111" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s">
+        <v>4</v>
+      </c>
+      <c r="F111" t="s">
+        <v>4</v>
+      </c>
       <c r="G111" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2298,6 +3093,21 @@
       <c r="A112">
         <v>108</v>
       </c>
+      <c r="B112" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
+        <v>5</v>
+      </c>
+      <c r="F112" t="s">
+        <v>4</v>
+      </c>
       <c r="G112" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2307,15 +3117,45 @@
       <c r="A113">
         <v>109</v>
       </c>
+      <c r="B113" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" t="s">
+        <v>3</v>
+      </c>
+      <c r="F113" t="s">
+        <v>5</v>
+      </c>
       <c r="G113" t="str">
         <f t="shared" si="1"/>
-        <v>Пользовватель не заригестрирован</v>
+        <v>Регистрация пользователя</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>110</v>
       </c>
+      <c r="B114" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" t="s">
+        <v>5</v>
+      </c>
       <c r="G114" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2325,6 +3165,21 @@
       <c r="A115">
         <v>111</v>
       </c>
+      <c r="B115" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" t="s">
+        <v>5</v>
+      </c>
+      <c r="F115" t="s">
+        <v>5</v>
+      </c>
       <c r="G115" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2334,15 +3189,45 @@
       <c r="A116">
         <v>112</v>
       </c>
+      <c r="B116" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" t="s">
+        <v>3</v>
+      </c>
+      <c r="F116" t="s">
+        <v>5</v>
+      </c>
       <c r="G116" t="str">
         <f t="shared" si="1"/>
-        <v>Пользовватель не заригестрирован</v>
+        <v>Регистрация пользователя</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>113</v>
       </c>
+      <c r="B117" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" t="s">
+        <v>5</v>
+      </c>
       <c r="G117" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2352,6 +3237,21 @@
       <c r="A118">
         <v>114</v>
       </c>
+      <c r="B118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" t="s">
+        <v>5</v>
+      </c>
+      <c r="F118" t="s">
+        <v>5</v>
+      </c>
       <c r="G118" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2361,6 +3261,21 @@
       <c r="A119">
         <v>115</v>
       </c>
+      <c r="B119" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" t="s">
+        <v>3</v>
+      </c>
+      <c r="F119" t="s">
+        <v>5</v>
+      </c>
       <c r="G119" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2370,6 +3285,21 @@
       <c r="A120">
         <v>116</v>
       </c>
+      <c r="B120" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" t="s">
+        <v>4</v>
+      </c>
+      <c r="F120" t="s">
+        <v>5</v>
+      </c>
       <c r="G120" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2379,6 +3309,21 @@
       <c r="A121">
         <v>117</v>
       </c>
+      <c r="B121" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" t="s">
+        <v>5</v>
+      </c>
+      <c r="F121" t="s">
+        <v>5</v>
+      </c>
       <c r="G121" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2388,6 +3333,21 @@
       <c r="A122">
         <v>118</v>
       </c>
+      <c r="B122" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" t="s">
+        <v>3</v>
+      </c>
+      <c r="F122" t="s">
+        <v>5</v>
+      </c>
       <c r="G122" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2397,6 +3357,21 @@
       <c r="A123">
         <v>119</v>
       </c>
+      <c r="B123" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" t="s">
+        <v>4</v>
+      </c>
+      <c r="F123" t="s">
+        <v>5</v>
+      </c>
       <c r="G123" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2406,6 +3381,21 @@
       <c r="A124">
         <v>120</v>
       </c>
+      <c r="B124" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>5</v>
+      </c>
+      <c r="F124" t="s">
+        <v>5</v>
+      </c>
       <c r="G124" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2415,6 +3405,21 @@
       <c r="A125">
         <v>121</v>
       </c>
+      <c r="B125" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" t="s">
+        <v>3</v>
+      </c>
+      <c r="F125" t="s">
+        <v>5</v>
+      </c>
       <c r="G125" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2424,6 +3429,21 @@
       <c r="A126">
         <v>122</v>
       </c>
+      <c r="B126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" t="s">
+        <v>5</v>
+      </c>
       <c r="G126" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2433,6 +3453,21 @@
       <c r="A127">
         <v>123</v>
       </c>
+      <c r="B127" t="s">
+        <v>3</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" t="s">
+        <v>5</v>
+      </c>
+      <c r="F127" t="s">
+        <v>5</v>
+      </c>
       <c r="G127" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2442,6 +3477,21 @@
       <c r="A128">
         <v>124</v>
       </c>
+      <c r="B128" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" t="s">
+        <v>3</v>
+      </c>
+      <c r="F128" t="s">
+        <v>5</v>
+      </c>
       <c r="G128" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2451,6 +3501,21 @@
       <c r="A129">
         <v>125</v>
       </c>
+      <c r="B129" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" t="s">
+        <v>4</v>
+      </c>
+      <c r="F129" t="s">
+        <v>5</v>
+      </c>
       <c r="G129" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2460,6 +3525,21 @@
       <c r="A130">
         <v>126</v>
       </c>
+      <c r="B130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" t="s">
+        <v>5</v>
+      </c>
+      <c r="F130" t="s">
+        <v>5</v>
+      </c>
       <c r="G130" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2469,6 +3549,21 @@
       <c r="A131">
         <v>127</v>
       </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" t="s">
+        <v>3</v>
+      </c>
+      <c r="F131" t="s">
+        <v>5</v>
+      </c>
       <c r="G131" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2478,6 +3573,21 @@
       <c r="A132">
         <v>128</v>
       </c>
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" t="s">
+        <v>4</v>
+      </c>
+      <c r="F132" t="s">
+        <v>5</v>
+      </c>
       <c r="G132" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2487,6 +3597,21 @@
       <c r="A133">
         <v>129</v>
       </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133" t="s">
+        <v>5</v>
+      </c>
+      <c r="F133" t="s">
+        <v>5</v>
+      </c>
       <c r="G133" t="str">
         <f t="shared" si="1"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2496,8 +3621,23 @@
       <c r="A134">
         <v>130</v>
       </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" t="s">
+        <v>3</v>
+      </c>
+      <c r="F134" t="s">
+        <v>5</v>
+      </c>
       <c r="G134" t="str">
-        <f t="shared" ref="G134:G149" si="2">IF(AND(B134="Заполнено корректно",C134="Заполнено корректно",E134="Заполнено корректно"),"Регистрация пользователя","Пользовватель не заригестрирован")</f>
+        <f t="shared" ref="G134:G166" si="2">IF(AND(B134="Заполнено корректно",C134="Заполнено корректно",E134="Заполнено корректно"),"Регистрация пользователя","Пользовватель не заригестрирован")</f>
         <v>Пользовватель не заригестрирован</v>
       </c>
     </row>
@@ -2505,6 +3645,21 @@
       <c r="A135">
         <v>131</v>
       </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" t="s">
+        <v>4</v>
+      </c>
+      <c r="F135" t="s">
+        <v>5</v>
+      </c>
       <c r="G135" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2514,6 +3669,21 @@
       <c r="A136">
         <v>132</v>
       </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" t="s">
+        <v>5</v>
+      </c>
+      <c r="F136" t="s">
+        <v>5</v>
+      </c>
       <c r="G136" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2523,6 +3693,21 @@
       <c r="A137">
         <v>133</v>
       </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137" t="s">
+        <v>3</v>
+      </c>
+      <c r="F137" t="s">
+        <v>5</v>
+      </c>
       <c r="G137" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2532,6 +3717,21 @@
       <c r="A138">
         <v>134</v>
       </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" t="s">
+        <v>4</v>
+      </c>
+      <c r="F138" t="s">
+        <v>5</v>
+      </c>
       <c r="G138" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2541,6 +3741,21 @@
       <c r="A139">
         <v>135</v>
       </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" t="s">
+        <v>5</v>
+      </c>
+      <c r="F139" t="s">
+        <v>5</v>
+      </c>
       <c r="G139" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2550,6 +3765,21 @@
       <c r="A140">
         <v>136</v>
       </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="s">
+        <v>4</v>
+      </c>
+      <c r="D140" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" t="s">
+        <v>3</v>
+      </c>
+      <c r="F140" t="s">
+        <v>5</v>
+      </c>
       <c r="G140" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2559,6 +3789,21 @@
       <c r="A141">
         <v>137</v>
       </c>
+      <c r="B141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" t="s">
+        <v>4</v>
+      </c>
+      <c r="F141" t="s">
+        <v>5</v>
+      </c>
       <c r="G141" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2568,6 +3813,21 @@
       <c r="A142">
         <v>138</v>
       </c>
+      <c r="B142" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>4</v>
+      </c>
+      <c r="D142" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" t="s">
+        <v>5</v>
+      </c>
+      <c r="F142" t="s">
+        <v>5</v>
+      </c>
       <c r="G142" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2577,6 +3837,21 @@
       <c r="A143">
         <v>139</v>
       </c>
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143" t="s">
+        <v>3</v>
+      </c>
+      <c r="F143" t="s">
+        <v>5</v>
+      </c>
       <c r="G143" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2586,6 +3861,21 @@
       <c r="A144">
         <v>140</v>
       </c>
+      <c r="B144" t="s">
+        <v>4</v>
+      </c>
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" t="s">
+        <v>5</v>
+      </c>
       <c r="G144" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2595,6 +3885,21 @@
       <c r="A145">
         <v>141</v>
       </c>
+      <c r="B145" t="s">
+        <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" t="s">
+        <v>5</v>
+      </c>
+      <c r="F145" t="s">
+        <v>5</v>
+      </c>
       <c r="G145" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2604,6 +3909,21 @@
       <c r="A146">
         <v>142</v>
       </c>
+      <c r="B146" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" t="s">
+        <v>3</v>
+      </c>
+      <c r="F146" t="s">
+        <v>5</v>
+      </c>
       <c r="G146" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2613,6 +3933,21 @@
       <c r="A147">
         <v>143</v>
       </c>
+      <c r="B147" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" t="s">
+        <v>4</v>
+      </c>
+      <c r="F147" t="s">
+        <v>5</v>
+      </c>
       <c r="G147" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2622,6 +3957,21 @@
       <c r="A148">
         <v>144</v>
       </c>
+      <c r="B148" t="s">
+        <v>4</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" t="s">
+        <v>5</v>
+      </c>
+      <c r="F148" t="s">
+        <v>5</v>
+      </c>
       <c r="G148" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
@@ -2631,7 +3981,430 @@
       <c r="A149">
         <v>145</v>
       </c>
+      <c r="B149" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" t="s">
+        <v>3</v>
+      </c>
+      <c r="F149" t="s">
+        <v>5</v>
+      </c>
       <c r="G149" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>146</v>
+      </c>
+      <c r="B150" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F150" t="s">
+        <v>5</v>
+      </c>
+      <c r="G150" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>147</v>
+      </c>
+      <c r="B151" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" t="s">
+        <v>5</v>
+      </c>
+      <c r="F151" t="s">
+        <v>5</v>
+      </c>
+      <c r="G151" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>148</v>
+      </c>
+      <c r="B152" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>3</v>
+      </c>
+      <c r="F152" t="s">
+        <v>5</v>
+      </c>
+      <c r="G152" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>149</v>
+      </c>
+      <c r="B153" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>4</v>
+      </c>
+      <c r="F153" t="s">
+        <v>5</v>
+      </c>
+      <c r="G153" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>150</v>
+      </c>
+      <c r="B154" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" t="s">
+        <v>5</v>
+      </c>
+      <c r="F154" t="s">
+        <v>5</v>
+      </c>
+      <c r="G154" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>151</v>
+      </c>
+      <c r="B155" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" t="s">
+        <v>4</v>
+      </c>
+      <c r="D155" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" t="s">
+        <v>3</v>
+      </c>
+      <c r="F155" t="s">
+        <v>5</v>
+      </c>
+      <c r="G155" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>152</v>
+      </c>
+      <c r="B156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" t="s">
+        <v>4</v>
+      </c>
+      <c r="D156" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" t="s">
+        <v>4</v>
+      </c>
+      <c r="F156" t="s">
+        <v>5</v>
+      </c>
+      <c r="G156" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>153</v>
+      </c>
+      <c r="B157" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" t="s">
+        <v>4</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" t="s">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
+        <v>5</v>
+      </c>
+      <c r="G157" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>154</v>
+      </c>
+      <c r="B158" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>3</v>
+      </c>
+      <c r="F158" t="s">
+        <v>5</v>
+      </c>
+      <c r="G158" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>155</v>
+      </c>
+      <c r="B159" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" t="s">
+        <v>4</v>
+      </c>
+      <c r="D159" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" t="s">
+        <v>4</v>
+      </c>
+      <c r="F159" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>156</v>
+      </c>
+      <c r="B160" t="s">
+        <v>5</v>
+      </c>
+      <c r="C160" t="s">
+        <v>4</v>
+      </c>
+      <c r="D160" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" t="s">
+        <v>5</v>
+      </c>
+      <c r="F160" t="s">
+        <v>5</v>
+      </c>
+      <c r="G160" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>157</v>
+      </c>
+      <c r="B161" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" t="s">
+        <v>3</v>
+      </c>
+      <c r="F161" t="s">
+        <v>5</v>
+      </c>
+      <c r="G161" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>158</v>
+      </c>
+      <c r="B162" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" t="s">
+        <v>4</v>
+      </c>
+      <c r="F162" t="s">
+        <v>5</v>
+      </c>
+      <c r="G162" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>159</v>
+      </c>
+      <c r="B163" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>10</v>
+      </c>
+      <c r="E163" t="s">
+        <v>5</v>
+      </c>
+      <c r="F163" t="s">
+        <v>5</v>
+      </c>
+      <c r="G163" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>160</v>
+      </c>
+      <c r="B164" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164" t="s">
+        <v>5</v>
+      </c>
+      <c r="D164" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" t="s">
+        <v>3</v>
+      </c>
+      <c r="F164" t="s">
+        <v>5</v>
+      </c>
+      <c r="G164" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>161</v>
+      </c>
+      <c r="B165" t="s">
+        <v>5</v>
+      </c>
+      <c r="C165" t="s">
+        <v>5</v>
+      </c>
+      <c r="D165" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" t="s">
+        <v>4</v>
+      </c>
+      <c r="F165" t="s">
+        <v>5</v>
+      </c>
+      <c r="G165" t="str">
+        <f t="shared" si="2"/>
+        <v>Пользовватель не заригестрирован</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>162</v>
+      </c>
+      <c r="B166" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" t="s">
+        <v>5</v>
+      </c>
+      <c r="F166" t="s">
+        <v>5</v>
+      </c>
+      <c r="G166" t="str">
         <f t="shared" si="2"/>
         <v>Пользовватель не заригестрирован</v>
       </c>
